--- a/service-flask/voluntariat_app/xlsx/template.xlsx
+++ b/service-flask/voluntariat_app/xlsx/template.xlsx
@@ -194,7 +194,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="AMH1:AMJ1"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AMH1" s="2"/>
